--- a/DATA/DGRAM Extranjerios_DocVigente_Estados.xlsx
+++ b/DATA/DGRAM Extranjerios_DocVigente_Estados.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bf48b3f04032ef9d/Documentos/SERVICIOS/PARKA/MIGRACIÓN/OFICINA/ALEX/IA-NAMI/BASES/DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\furbina\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{50094B65-0D50-4BD9-85DA-02EE83C30518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88F8FB4D-ECA6-4713-AC3A-8378100BF011}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488EEA47-1595-4008-AC5E-5008DBFF64EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{351A603F-E80E-478E-A9D1-953FCB364CAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{351A603F-E80E-478E-A9D1-953FCB364CAC}"/>
   </bookViews>
   <sheets>
-    <sheet name="EstadísticasEdos" sheetId="1" r:id="rId1"/>
+    <sheet name="EstadísticasEdo" sheetId="2" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
+    <definedName name="Condado" localSheetId="0">'[1]Listado Municipios'!#REF!:INDEX('[1]Listado Municipios'!#REF!,COUNTA('[1]Listado Municipios'!#REF!))</definedName>
     <definedName name="Condado">'[1]Listado Municipios'!#REF!:INDEX('[1]Listado Municipios'!#REF!,COUNTA('[1]Listado Municipios'!#REF!))</definedName>
+    <definedName name="Total" localSheetId="0">'[1]Listado Municipios'!#REF!:INDEX('[1]Listado Municipios'!#REF!,COUNTA('[1]Listado Municipios'!#REF!))</definedName>
     <definedName name="Total">'[1]Listado Municipios'!#REF!:INDEX('[1]Listado Municipios'!#REF!,COUNTA('[1]Listado Municipios'!#REF!))</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,8 +36,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -370,6 +370,18 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -386,18 +398,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -418,7 +418,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Hoja2"/>
@@ -473,9 +473,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -513,7 +513,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -619,7 +619,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -761,71 +761,71 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF6919CE-216F-47F7-B445-3573C8D814E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBEA4134-6961-413B-8F21-516631814FA2}">
   <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="15" t="s">
+      <c r="B1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="16" t="s">
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="17" t="s">
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="18" t="s">
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="19" t="s">
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="20" t="s">
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="21" t="s">
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
     </row>
-    <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13"/>
+    <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -899,54 +899,54 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="10">
-        <v>4522</v>
+        <v>4551</v>
       </c>
       <c r="C3" s="10">
-        <v>3226</v>
+        <v>3243</v>
       </c>
       <c r="D3" s="11">
-        <v>7748</v>
+        <v>7794</v>
       </c>
       <c r="E3" s="10">
-        <v>3399</v>
+        <v>3408</v>
       </c>
       <c r="F3" s="10">
-        <v>2584</v>
+        <v>2593</v>
       </c>
       <c r="G3" s="11">
-        <v>5983</v>
+        <v>6001</v>
       </c>
       <c r="H3" s="10">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="I3" s="10">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="J3" s="11">
-        <v>1615</v>
+        <v>1639</v>
       </c>
       <c r="K3" s="10">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L3" s="10">
         <v>59</v>
       </c>
       <c r="M3" s="11">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N3" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O3" s="10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P3" s="11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="10">
         <v>0</v>
@@ -976,54 +976,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="10">
-        <v>27650</v>
+        <v>27771</v>
       </c>
       <c r="C4" s="10">
-        <v>21598</v>
+        <v>21684</v>
       </c>
       <c r="D4" s="11">
-        <v>49248</v>
+        <v>49455</v>
       </c>
       <c r="E4" s="10">
-        <v>23034</v>
+        <v>23113</v>
       </c>
       <c r="F4" s="10">
-        <v>18450</v>
+        <v>18516</v>
       </c>
       <c r="G4" s="11">
-        <v>41484</v>
+        <v>41629</v>
       </c>
       <c r="H4" s="10">
-        <v>4238</v>
+        <v>4267</v>
       </c>
       <c r="I4" s="10">
-        <v>2876</v>
+        <v>2883</v>
       </c>
       <c r="J4" s="11">
-        <v>7114</v>
+        <v>7150</v>
       </c>
       <c r="K4" s="10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L4" s="10">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M4" s="11">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="N4" s="10">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="O4" s="10">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="P4" s="11">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="Q4" s="10">
         <v>0</v>
@@ -1053,45 +1053,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="10">
-        <v>17476</v>
+        <v>17514</v>
       </c>
       <c r="C5" s="10">
-        <v>14958</v>
+        <v>14990</v>
       </c>
       <c r="D5" s="11">
-        <v>32434</v>
+        <v>32504</v>
       </c>
       <c r="E5" s="10">
-        <v>13583</v>
+        <v>13647</v>
       </c>
       <c r="F5" s="10">
-        <v>11470</v>
+        <v>11528</v>
       </c>
       <c r="G5" s="11">
-        <v>25053</v>
+        <v>25175</v>
       </c>
       <c r="H5" s="10">
-        <v>3802</v>
+        <v>3775</v>
       </c>
       <c r="I5" s="10">
-        <v>3382</v>
+        <v>3355</v>
       </c>
       <c r="J5" s="11">
-        <v>7184</v>
+        <v>7130</v>
       </c>
       <c r="K5" s="10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L5" s="10">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M5" s="11">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N5" s="10">
         <v>55</v>
@@ -1130,54 +1130,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="10">
-        <v>3690</v>
+        <v>3693</v>
       </c>
       <c r="C6" s="10">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="D6" s="11">
-        <v>6634</v>
+        <v>6636</v>
       </c>
       <c r="E6" s="10">
-        <v>2764</v>
+        <v>2775</v>
       </c>
       <c r="F6" s="10">
-        <v>2395</v>
+        <v>2402</v>
       </c>
       <c r="G6" s="11">
-        <v>5159</v>
+        <v>5177</v>
       </c>
       <c r="H6" s="10">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="I6" s="10">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="J6" s="11">
-        <v>1354</v>
+        <v>1338</v>
       </c>
       <c r="K6" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="10">
         <v>14</v>
       </c>
       <c r="M6" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N6" s="10">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O6" s="10">
         <v>46</v>
       </c>
       <c r="P6" s="11">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q6" s="10">
         <v>0</v>
@@ -1207,36 +1207,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="10">
-        <v>213968</v>
+        <v>214372</v>
       </c>
       <c r="C7" s="10">
-        <v>198083</v>
+        <v>198662</v>
       </c>
       <c r="D7" s="11">
-        <v>412051</v>
+        <v>413034</v>
       </c>
       <c r="E7" s="10">
-        <v>70664</v>
+        <v>71097</v>
       </c>
       <c r="F7" s="10">
-        <v>64049</v>
+        <v>64466</v>
       </c>
       <c r="G7" s="11">
-        <v>134713</v>
+        <v>135563</v>
       </c>
       <c r="H7" s="10">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="I7" s="10">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="J7" s="11">
-        <v>899</v>
+        <v>921</v>
       </c>
       <c r="K7" s="10">
         <v>57</v>
@@ -1248,13 +1248,13 @@
         <v>165</v>
       </c>
       <c r="N7" s="10">
-        <v>4356</v>
+        <v>4467</v>
       </c>
       <c r="O7" s="10">
-        <v>3442</v>
+        <v>3608</v>
       </c>
       <c r="P7" s="11">
-        <v>7798</v>
+        <v>8075</v>
       </c>
       <c r="Q7" s="10">
         <v>0</v>
@@ -1266,72 +1266,72 @@
         <v>0</v>
       </c>
       <c r="T7" s="10">
-        <v>136359</v>
+        <v>136265</v>
       </c>
       <c r="U7" s="10">
-        <v>129638</v>
+        <v>129640</v>
       </c>
       <c r="V7" s="11">
-        <v>265997</v>
+        <v>265905</v>
       </c>
       <c r="W7" s="10">
-        <v>2007</v>
+        <v>1945</v>
       </c>
       <c r="X7" s="10">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="Y7" s="11">
-        <v>2479</v>
+        <v>2405</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="10">
-        <v>6762</v>
+        <v>6801</v>
       </c>
       <c r="C8" s="10">
-        <v>4644</v>
+        <v>4674</v>
       </c>
       <c r="D8" s="11">
-        <v>11406</v>
+        <v>11475</v>
       </c>
       <c r="E8" s="10">
-        <v>4724</v>
+        <v>4746</v>
       </c>
       <c r="F8" s="10">
-        <v>3552</v>
+        <v>3572</v>
       </c>
       <c r="G8" s="11">
-        <v>8276</v>
+        <v>8318</v>
       </c>
       <c r="H8" s="10">
-        <v>1863</v>
+        <v>1875</v>
       </c>
       <c r="I8" s="10">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="J8" s="11">
-        <v>2774</v>
+        <v>2794</v>
       </c>
       <c r="K8" s="10">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L8" s="10">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" s="11">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N8" s="10">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="O8" s="10">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P8" s="11">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q8" s="10">
         <v>0</v>
@@ -1361,54 +1361,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="10">
-        <v>96898</v>
+        <v>97904</v>
       </c>
       <c r="C9" s="10">
-        <v>90631</v>
+        <v>91400</v>
       </c>
       <c r="D9" s="11">
-        <v>187529</v>
+        <v>189304</v>
       </c>
       <c r="E9" s="10">
-        <v>70227</v>
+        <v>70579</v>
       </c>
       <c r="F9" s="10">
-        <v>69084</v>
+        <v>69385</v>
       </c>
       <c r="G9" s="11">
-        <v>139311</v>
+        <v>139964</v>
       </c>
       <c r="H9" s="10">
-        <v>23772</v>
+        <v>24308</v>
       </c>
       <c r="I9" s="10">
-        <v>18740</v>
+        <v>19113</v>
       </c>
       <c r="J9" s="11">
-        <v>42512</v>
+        <v>43421</v>
       </c>
       <c r="K9" s="10">
-        <v>1624</v>
+        <v>1672</v>
       </c>
       <c r="L9" s="10">
-        <v>1768</v>
+        <v>1801</v>
       </c>
       <c r="M9" s="11">
-        <v>3392</v>
+        <v>3473</v>
       </c>
       <c r="N9" s="10">
-        <v>1273</v>
+        <v>1343</v>
       </c>
       <c r="O9" s="10">
-        <v>1039</v>
+        <v>1101</v>
       </c>
       <c r="P9" s="11">
-        <v>2312</v>
+        <v>2444</v>
       </c>
       <c r="Q9" s="10">
         <v>2</v>
@@ -1438,54 +1438,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="10">
-        <v>9396</v>
+        <v>9428</v>
       </c>
       <c r="C10" s="10">
-        <v>6380</v>
+        <v>6414</v>
       </c>
       <c r="D10" s="11">
-        <v>15776</v>
+        <v>15842</v>
       </c>
       <c r="E10" s="10">
-        <v>7026</v>
+        <v>7042</v>
       </c>
       <c r="F10" s="10">
-        <v>5239</v>
+        <v>5262</v>
       </c>
       <c r="G10" s="11">
-        <v>12265</v>
+        <v>12304</v>
       </c>
       <c r="H10" s="10">
-        <v>2292</v>
+        <v>2308</v>
       </c>
       <c r="I10" s="10">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="J10" s="11">
-        <v>3351</v>
+        <v>3376</v>
       </c>
       <c r="K10" s="10">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L10" s="10">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M10" s="11">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N10" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O10" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P10" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q10" s="10">
         <v>0</v>
@@ -1515,36 +1515,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="10">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="C11" s="10">
-        <v>1587</v>
+        <v>1590</v>
       </c>
       <c r="D11" s="11">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="E11" s="10">
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="F11" s="10">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="G11" s="11">
-        <v>3130</v>
+        <v>3138</v>
       </c>
       <c r="H11" s="10">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="I11" s="10">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J11" s="11">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="K11" s="10">
         <v>7</v>
@@ -1592,36 +1592,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="10">
-        <v>1520</v>
+        <v>1513</v>
       </c>
       <c r="C12" s="10">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D12" s="11">
-        <v>2523</v>
+        <v>2517</v>
       </c>
       <c r="E12" s="10">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F12" s="10">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="G12" s="11">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="H12" s="10">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="I12" s="10">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J12" s="11">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K12" s="10">
         <v>8</v>
@@ -1669,54 +1669,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="10">
-        <v>16426</v>
+        <v>16611</v>
       </c>
       <c r="C13" s="10">
-        <v>17321</v>
+        <v>17499</v>
       </c>
       <c r="D13" s="11">
-        <v>33747</v>
+        <v>34110</v>
       </c>
       <c r="E13" s="10">
-        <v>13462</v>
+        <v>13499</v>
       </c>
       <c r="F13" s="10">
-        <v>14822</v>
+        <v>14863</v>
       </c>
       <c r="G13" s="11">
-        <v>28284</v>
+        <v>28362</v>
       </c>
       <c r="H13" s="10">
-        <v>2444</v>
+        <v>2494</v>
       </c>
       <c r="I13" s="10">
-        <v>1979</v>
+        <v>2008</v>
       </c>
       <c r="J13" s="11">
-        <v>4423</v>
+        <v>4502</v>
       </c>
       <c r="K13" s="10">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L13" s="10">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="M13" s="11">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="N13" s="10">
-        <v>352</v>
+        <v>447</v>
       </c>
       <c r="O13" s="10">
-        <v>372</v>
+        <v>476</v>
       </c>
       <c r="P13" s="11">
-        <v>724</v>
+        <v>923</v>
       </c>
       <c r="Q13" s="10">
         <v>1</v>
@@ -1746,45 +1746,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="10">
-        <v>15224</v>
+        <v>15275</v>
       </c>
       <c r="C14" s="10">
-        <v>13189</v>
+        <v>13208</v>
       </c>
       <c r="D14" s="11">
-        <v>28413</v>
+        <v>28483</v>
       </c>
       <c r="E14" s="10">
-        <v>11717</v>
+        <v>11743</v>
       </c>
       <c r="F14" s="10">
-        <v>10473</v>
+        <v>10497</v>
       </c>
       <c r="G14" s="11">
-        <v>22190</v>
+        <v>22240</v>
       </c>
       <c r="H14" s="10">
-        <v>3381</v>
+        <v>3402</v>
       </c>
       <c r="I14" s="10">
-        <v>2581</v>
+        <v>2574</v>
       </c>
       <c r="J14" s="11">
-        <v>5962</v>
+        <v>5976</v>
       </c>
       <c r="K14" s="10">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="L14" s="10">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M14" s="11">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="N14" s="10">
         <v>7</v>
@@ -1823,54 +1823,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="10">
-        <v>2890</v>
+        <v>2888</v>
       </c>
       <c r="C15" s="10">
-        <v>2391</v>
+        <v>2401</v>
       </c>
       <c r="D15" s="11">
-        <v>5281</v>
+        <v>5289</v>
       </c>
       <c r="E15" s="10">
-        <v>2296</v>
+        <v>2300</v>
       </c>
       <c r="F15" s="10">
-        <v>1785</v>
+        <v>1790</v>
       </c>
       <c r="G15" s="11">
-        <v>4081</v>
+        <v>4090</v>
       </c>
       <c r="H15" s="10">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="I15" s="10">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="J15" s="11">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="K15" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" s="10">
         <v>21</v>
       </c>
       <c r="M15" s="11">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N15" s="10">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O15" s="10">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P15" s="11">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q15" s="10">
         <v>0</v>
@@ -1900,54 +1900,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="10">
-        <v>4316</v>
+        <v>4381</v>
       </c>
       <c r="C16" s="10">
-        <v>3758</v>
+        <v>3856</v>
       </c>
       <c r="D16" s="11">
-        <v>8074</v>
+        <v>8237</v>
       </c>
       <c r="E16" s="10">
-        <v>3177</v>
+        <v>3189</v>
       </c>
       <c r="F16" s="10">
-        <v>2790</v>
+        <v>2809</v>
       </c>
       <c r="G16" s="11">
-        <v>5967</v>
+        <v>5998</v>
       </c>
       <c r="H16" s="10">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="I16" s="10">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="J16" s="11">
-        <v>1836</v>
+        <v>1860</v>
       </c>
       <c r="K16" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L16" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M16" s="11">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N16" s="10">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="O16" s="10">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="P16" s="11">
-        <v>213</v>
+        <v>318</v>
       </c>
       <c r="Q16" s="10">
         <v>0</v>
@@ -1977,54 +1977,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="10">
-        <v>37688</v>
+        <v>37845</v>
       </c>
       <c r="C17" s="10">
-        <v>31036</v>
+        <v>31166</v>
       </c>
       <c r="D17" s="11">
-        <v>68724</v>
+        <v>69011</v>
       </c>
       <c r="E17" s="10">
-        <v>30112</v>
+        <v>30253</v>
       </c>
       <c r="F17" s="10">
-        <v>25065</v>
+        <v>25194</v>
       </c>
       <c r="G17" s="11">
-        <v>55177</v>
+        <v>55447</v>
       </c>
       <c r="H17" s="10">
-        <v>7038</v>
+        <v>7043</v>
       </c>
       <c r="I17" s="10">
-        <v>5264</v>
+        <v>5260</v>
       </c>
       <c r="J17" s="11">
-        <v>12302</v>
+        <v>12303</v>
       </c>
       <c r="K17" s="10">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="L17" s="10">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="M17" s="11">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="N17" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O17" s="10">
         <v>4</v>
       </c>
       <c r="P17" s="11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="10">
         <v>0</v>
@@ -2054,45 +2054,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="10">
-        <v>3416</v>
+        <v>3431</v>
       </c>
       <c r="C18" s="10">
-        <v>2880</v>
+        <v>2902</v>
       </c>
       <c r="D18" s="11">
-        <v>6296</v>
+        <v>6333</v>
       </c>
       <c r="E18" s="10">
-        <v>2729</v>
+        <v>2740</v>
       </c>
       <c r="F18" s="10">
-        <v>2309</v>
+        <v>2322</v>
       </c>
       <c r="G18" s="11">
-        <v>5038</v>
+        <v>5062</v>
       </c>
       <c r="H18" s="10">
         <v>528</v>
       </c>
       <c r="I18" s="10">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="J18" s="11">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="K18" s="10">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L18" s="10">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M18" s="11">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N18" s="10">
         <v>76</v>
@@ -2131,45 +2131,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="10">
-        <v>3505</v>
+        <v>3540</v>
       </c>
       <c r="C19" s="10">
-        <v>3694</v>
+        <v>3718</v>
       </c>
       <c r="D19" s="11">
-        <v>7199</v>
+        <v>7258</v>
       </c>
       <c r="E19" s="10">
-        <v>2848</v>
+        <v>2863</v>
       </c>
       <c r="F19" s="10">
-        <v>3129</v>
+        <v>3144</v>
       </c>
       <c r="G19" s="11">
-        <v>5977</v>
+        <v>6007</v>
       </c>
       <c r="H19" s="10">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="I19" s="10">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="J19" s="11">
-        <v>996</v>
+        <v>1024</v>
       </c>
       <c r="K19" s="10">
         <v>81</v>
       </c>
       <c r="L19" s="10">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M19" s="11">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N19" s="10">
         <v>29</v>
@@ -2208,36 +2208,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="10">
-        <v>8487</v>
+        <v>8518</v>
       </c>
       <c r="C20" s="10">
-        <v>7781</v>
+        <v>7795</v>
       </c>
       <c r="D20" s="11">
-        <v>16268</v>
+        <v>16313</v>
       </c>
       <c r="E20" s="10">
-        <v>6205</v>
+        <v>6244</v>
       </c>
       <c r="F20" s="10">
-        <v>5602</v>
+        <v>5637</v>
       </c>
       <c r="G20" s="11">
-        <v>11807</v>
+        <v>11881</v>
       </c>
       <c r="H20" s="10">
-        <v>2210</v>
+        <v>2201</v>
       </c>
       <c r="I20" s="10">
-        <v>2104</v>
+        <v>2082</v>
       </c>
       <c r="J20" s="11">
-        <v>4314</v>
+        <v>4283</v>
       </c>
       <c r="K20" s="10">
         <v>10</v>
@@ -2249,13 +2249,13 @@
         <v>15</v>
       </c>
       <c r="N20" s="10">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O20" s="10">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P20" s="11">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q20" s="10">
         <v>0</v>
@@ -2285,54 +2285,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="10">
-        <v>23912</v>
+        <v>24100</v>
       </c>
       <c r="C21" s="10">
-        <v>18766</v>
+        <v>18911</v>
       </c>
       <c r="D21" s="11">
-        <v>42678</v>
+        <v>43011</v>
       </c>
       <c r="E21" s="10">
-        <v>17163</v>
+        <v>17265</v>
       </c>
       <c r="F21" s="10">
-        <v>14896</v>
+        <v>14968</v>
       </c>
       <c r="G21" s="11">
-        <v>32059</v>
+        <v>32233</v>
       </c>
       <c r="H21" s="10">
-        <v>5868</v>
+        <v>5932</v>
       </c>
       <c r="I21" s="10">
-        <v>3101</v>
+        <v>3168</v>
       </c>
       <c r="J21" s="11">
-        <v>8969</v>
+        <v>9100</v>
       </c>
       <c r="K21" s="10">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="L21" s="10">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="M21" s="11">
-        <v>1571</v>
+        <v>1594</v>
       </c>
       <c r="N21" s="10">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O21" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P21" s="11">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Q21" s="10">
         <v>0</v>
@@ -2362,54 +2362,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="10">
-        <v>5965</v>
+        <v>5977</v>
       </c>
       <c r="C22" s="10">
-        <v>5793</v>
+        <v>5818</v>
       </c>
       <c r="D22" s="11">
-        <v>11758</v>
+        <v>11795</v>
       </c>
       <c r="E22" s="10">
-        <v>4592</v>
+        <v>4606</v>
       </c>
       <c r="F22" s="10">
-        <v>4464</v>
+        <v>4477</v>
       </c>
       <c r="G22" s="11">
-        <v>9056</v>
+        <v>9083</v>
       </c>
       <c r="H22" s="10">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="I22" s="10">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="J22" s="11">
-        <v>2456</v>
+        <v>2459</v>
       </c>
       <c r="K22" s="10">
         <v>25</v>
       </c>
       <c r="L22" s="10">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M22" s="11">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N22" s="10">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O22" s="10">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P22" s="11">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q22" s="10">
         <v>0</v>
@@ -2439,54 +2439,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="10">
-        <v>9151</v>
+        <v>9226</v>
       </c>
       <c r="C23" s="10">
-        <v>8548</v>
+        <v>8574</v>
       </c>
       <c r="D23" s="11">
-        <v>17699</v>
+        <v>17800</v>
       </c>
       <c r="E23" s="10">
-        <v>7112</v>
+        <v>7152</v>
       </c>
       <c r="F23" s="10">
-        <v>6839</v>
+        <v>6864</v>
       </c>
       <c r="G23" s="11">
-        <v>13951</v>
+        <v>14016</v>
       </c>
       <c r="H23" s="10">
-        <v>1583</v>
+        <v>1608</v>
       </c>
       <c r="I23" s="10">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="J23" s="11">
-        <v>2796</v>
+        <v>2819</v>
       </c>
       <c r="K23" s="10">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="L23" s="10">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M23" s="11">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="N23" s="10">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O23" s="10">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P23" s="11">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q23" s="10">
         <v>0</v>
@@ -2516,45 +2516,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="10">
-        <v>12992</v>
+        <v>13083</v>
       </c>
       <c r="C24" s="10">
-        <v>11066</v>
+        <v>11141</v>
       </c>
       <c r="D24" s="11">
-        <v>24058</v>
+        <v>24224</v>
       </c>
       <c r="E24" s="10">
-        <v>9595</v>
+        <v>9643</v>
       </c>
       <c r="F24" s="10">
-        <v>8579</v>
+        <v>8622</v>
       </c>
       <c r="G24" s="11">
-        <v>18174</v>
+        <v>18265</v>
       </c>
       <c r="H24" s="10">
-        <v>3198</v>
+        <v>3238</v>
       </c>
       <c r="I24" s="10">
-        <v>2333</v>
+        <v>2364</v>
       </c>
       <c r="J24" s="11">
-        <v>5531</v>
+        <v>5602</v>
       </c>
       <c r="K24" s="10">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="L24" s="10">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M24" s="11">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="N24" s="10">
         <v>2</v>
@@ -2593,54 +2593,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="10">
-        <v>54444</v>
+        <v>54763</v>
       </c>
       <c r="C25" s="10">
-        <v>58129</v>
+        <v>58473</v>
       </c>
       <c r="D25" s="11">
-        <v>112573</v>
+        <v>113236</v>
       </c>
       <c r="E25" s="10">
-        <v>32994</v>
+        <v>33156</v>
       </c>
       <c r="F25" s="10">
-        <v>34265</v>
+        <v>34422</v>
       </c>
       <c r="G25" s="11">
-        <v>67259</v>
+        <v>67578</v>
       </c>
       <c r="H25" s="10">
-        <v>10150</v>
+        <v>10145</v>
       </c>
       <c r="I25" s="10">
-        <v>9539</v>
+        <v>9538</v>
       </c>
       <c r="J25" s="11">
-        <v>19689</v>
+        <v>19683</v>
       </c>
       <c r="K25" s="10">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="L25" s="10">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="M25" s="11">
-        <v>1038</v>
+        <v>1070</v>
       </c>
       <c r="N25" s="10">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="O25" s="10">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="P25" s="11">
-        <v>373</v>
+        <v>477</v>
       </c>
       <c r="Q25" s="10">
         <v>0</v>
@@ -2652,13 +2652,13 @@
         <v>0</v>
       </c>
       <c r="T25" s="10">
-        <v>10715</v>
+        <v>10816</v>
       </c>
       <c r="U25" s="10">
-        <v>13495</v>
+        <v>13608</v>
       </c>
       <c r="V25" s="11">
-        <v>24210</v>
+        <v>24424</v>
       </c>
       <c r="W25" s="10">
         <v>3</v>
@@ -2670,54 +2670,54 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="10">
-        <v>7141</v>
+        <v>7166</v>
       </c>
       <c r="C26" s="10">
-        <v>4114</v>
+        <v>4134</v>
       </c>
       <c r="D26" s="11">
-        <v>11255</v>
+        <v>11300</v>
       </c>
       <c r="E26" s="10">
-        <v>4856</v>
+        <v>4872</v>
       </c>
       <c r="F26" s="10">
-        <v>2889</v>
+        <v>2900</v>
       </c>
       <c r="G26" s="11">
-        <v>7745</v>
+        <v>7772</v>
       </c>
       <c r="H26" s="10">
-        <v>2088</v>
+        <v>2099</v>
       </c>
       <c r="I26" s="10">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="J26" s="11">
-        <v>3105</v>
+        <v>3124</v>
       </c>
       <c r="K26" s="10">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L26" s="10">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="M26" s="11">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="N26" s="10">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O26" s="10">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P26" s="11">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Q26" s="10">
         <v>0</v>
@@ -2747,54 +2747,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="10">
-        <v>5940</v>
+        <v>5947</v>
       </c>
       <c r="C27" s="10">
-        <v>4520</v>
+        <v>4523</v>
       </c>
       <c r="D27" s="11">
-        <v>10460</v>
+        <v>10470</v>
       </c>
       <c r="E27" s="10">
-        <v>4894</v>
+        <v>4910</v>
       </c>
       <c r="F27" s="10">
-        <v>3651</v>
+        <v>3667</v>
       </c>
       <c r="G27" s="11">
-        <v>8545</v>
+        <v>8577</v>
       </c>
       <c r="H27" s="10">
-        <v>971</v>
+        <v>962</v>
       </c>
       <c r="I27" s="10">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="J27" s="11">
-        <v>1757</v>
+        <v>1734</v>
       </c>
       <c r="K27" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L27" s="10">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M27" s="11">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N27" s="10">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O27" s="10">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P27" s="11">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Q27" s="10">
         <v>0</v>
@@ -2824,54 +2824,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="10">
-        <v>8533</v>
+        <v>8543</v>
       </c>
       <c r="C28" s="10">
-        <v>6206</v>
+        <v>6223</v>
       </c>
       <c r="D28" s="11">
-        <v>14739</v>
+        <v>14766</v>
       </c>
       <c r="E28" s="10">
-        <v>7047</v>
+        <v>7065</v>
       </c>
       <c r="F28" s="10">
-        <v>5011</v>
+        <v>5029</v>
       </c>
       <c r="G28" s="11">
-        <v>12058</v>
+        <v>12094</v>
       </c>
       <c r="H28" s="10">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="I28" s="10">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="J28" s="11">
-        <v>2420</v>
+        <v>2416</v>
       </c>
       <c r="K28" s="10">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L28" s="10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M28" s="11">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N28" s="10">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O28" s="10">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P28" s="11">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="Q28" s="10">
         <v>3</v>
@@ -2901,36 +2901,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="10">
-        <v>17779</v>
+        <v>17794</v>
       </c>
       <c r="C29" s="10">
-        <v>14453</v>
+        <v>14458</v>
       </c>
       <c r="D29" s="11">
-        <v>32232</v>
+        <v>32252</v>
       </c>
       <c r="E29" s="10">
-        <v>9939</v>
+        <v>9967</v>
       </c>
       <c r="F29" s="10">
-        <v>8785</v>
+        <v>8797</v>
       </c>
       <c r="G29" s="11">
-        <v>18724</v>
+        <v>18764</v>
       </c>
       <c r="H29" s="10">
-        <v>966</v>
+        <v>1003</v>
       </c>
       <c r="I29" s="10">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="J29" s="11">
-        <v>1438</v>
+        <v>1508</v>
       </c>
       <c r="K29" s="10">
         <v>31</v>
@@ -2942,13 +2942,13 @@
         <v>72</v>
       </c>
       <c r="N29" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O29" s="10">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P29" s="11">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q29" s="10">
         <v>0</v>
@@ -2960,72 +2960,72 @@
         <v>0</v>
       </c>
       <c r="T29" s="10">
-        <v>5217</v>
+        <v>5150</v>
       </c>
       <c r="U29" s="10">
-        <v>5117</v>
+        <v>5075</v>
       </c>
       <c r="V29" s="11">
-        <v>10334</v>
+        <v>10225</v>
       </c>
       <c r="W29" s="10">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="X29" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29" s="11">
-        <v>1607</v>
+        <v>1620</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B30" s="10">
-        <v>5356</v>
+        <v>5408</v>
       </c>
       <c r="C30" s="10">
-        <v>3984</v>
+        <v>4005</v>
       </c>
       <c r="D30" s="11">
-        <v>9340</v>
+        <v>9413</v>
       </c>
       <c r="E30" s="10">
-        <v>4239</v>
+        <v>4248</v>
       </c>
       <c r="F30" s="10">
-        <v>3489</v>
+        <v>3498</v>
       </c>
       <c r="G30" s="11">
-        <v>7728</v>
+        <v>7746</v>
       </c>
       <c r="H30" s="10">
-        <v>1022</v>
+        <v>1064</v>
       </c>
       <c r="I30" s="10">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="J30" s="11">
-        <v>1437</v>
+        <v>1488</v>
       </c>
       <c r="K30" s="10">
         <v>28</v>
       </c>
       <c r="L30" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M30" s="11">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N30" s="10">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O30" s="10">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P30" s="11">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="10">
         <v>0</v>
@@ -3055,36 +3055,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B31" s="10">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C31" s="10">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="D31" s="11">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="E31" s="10">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="F31" s="10">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G31" s="11">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="H31" s="10">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I31" s="10">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J31" s="11">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="K31" s="10">
         <v>9</v>
@@ -3099,10 +3099,10 @@
         <v>53</v>
       </c>
       <c r="O31" s="10">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="P31" s="11">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Q31" s="10">
         <v>0</v>
@@ -3132,54 +3132,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="10">
-        <v>8421</v>
+        <v>8454</v>
       </c>
       <c r="C32" s="10">
-        <v>7023</v>
+        <v>7041</v>
       </c>
       <c r="D32" s="11">
-        <v>15444</v>
+        <v>15495</v>
       </c>
       <c r="E32" s="10">
-        <v>7124</v>
+        <v>7143</v>
       </c>
       <c r="F32" s="10">
-        <v>5912</v>
+        <v>5927</v>
       </c>
       <c r="G32" s="11">
-        <v>13036</v>
+        <v>13070</v>
       </c>
       <c r="H32" s="10">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="I32" s="10">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="J32" s="11">
-        <v>1811</v>
+        <v>1819</v>
       </c>
       <c r="K32" s="10">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L32" s="10">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="M32" s="11">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="N32" s="10">
         <v>154</v>
       </c>
       <c r="O32" s="10">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P32" s="11">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q32" s="10">
         <v>0</v>
@@ -3209,54 +3209,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B33" s="10">
-        <v>14143</v>
+        <v>14307</v>
       </c>
       <c r="C33" s="10">
-        <v>14206</v>
+        <v>14388</v>
       </c>
       <c r="D33" s="11">
-        <v>28349</v>
+        <v>28695</v>
       </c>
       <c r="E33" s="10">
-        <v>10093</v>
+        <v>10194</v>
       </c>
       <c r="F33" s="10">
-        <v>10096</v>
+        <v>10208</v>
       </c>
       <c r="G33" s="11">
-        <v>20189</v>
+        <v>20402</v>
       </c>
       <c r="H33" s="10">
-        <v>3734</v>
+        <v>3726</v>
       </c>
       <c r="I33" s="10">
-        <v>3633</v>
+        <v>3616</v>
       </c>
       <c r="J33" s="11">
-        <v>7367</v>
+        <v>7342</v>
       </c>
       <c r="K33" s="10">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="L33" s="10">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="M33" s="11">
-        <v>764</v>
+        <v>801</v>
       </c>
       <c r="N33" s="10">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="O33" s="10">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="P33" s="11">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="Q33" s="10">
         <v>0</v>
@@ -3286,54 +3286,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B34" s="10">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C34" s="10">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D34" s="11">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="E34" s="10">
         <v>963</v>
       </c>
       <c r="F34" s="10">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G34" s="11">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H34" s="10">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I34" s="10">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J34" s="11">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="K34" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L34" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M34" s="11">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N34" s="10">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O34" s="10">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P34" s="11">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Q34" s="10">
         <v>0</v>
@@ -3365,15 +3365,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="W1:Y1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="W1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
